--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLIII/LTAIPT_A63F43A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLIII/LTAIPT_A63F43A.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="136">
   <si>
     <t>49014</t>
   </si>
@@ -142,7 +142,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t>Ingresos por Venta de Bienes, Prestación de Servicios y Otros Ingresos</t>
@@ -163,266 +163,265 @@
     <t/>
   </si>
   <si>
+    <t>Productos</t>
+  </si>
+  <si>
+    <t>Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Aprovechamientos</t>
+  </si>
+  <si>
     <t>Transferencias, Asignaciones, Subsidios y Otras Ayudas</t>
   </si>
   <si>
     <t>Subsidios y Subvenciones</t>
   </si>
   <si>
+    <t>Recursos Estatales</t>
+  </si>
+  <si>
+    <t>58517</t>
+  </si>
+  <si>
     <t>Recursos Federales</t>
   </si>
   <si>
     <t>Subsecretaría de Educación Media Superior</t>
   </si>
   <si>
-    <t>Productos</t>
-  </si>
-  <si>
-    <t>Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Derechos</t>
-  </si>
-  <si>
-    <t>Derechos por Prestación de Servicios</t>
-  </si>
-  <si>
-    <t>Participaciones, Aportaciones, Convenios, Incentivos Derivados de la Colaboración Fiscal y
-Fondos Distintos de Aportaciones</t>
-  </si>
-  <si>
-    <t>Aportaciones</t>
-  </si>
-  <si>
-    <t>105662</t>
-  </si>
-  <si>
-    <t>Transferencias Federales Etiquetadas</t>
-  </si>
-  <si>
-    <t>166667</t>
-  </si>
-  <si>
-    <t>Recursos Estatales</t>
-  </si>
-  <si>
-    <t>9E598A861F1C170CCC0F7CFE5AFC3F62</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>5022335.36</t>
-  </si>
-  <si>
-    <t>11/08/2022</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Depto.%20de%20Programacion%20y%20Presupuesto/3er_Trimestre/Informacion%20Presupuestal/presupuestal_3er_trimestre.pdf</t>
-  </si>
-  <si>
-    <t>17/10/2022</t>
-  </si>
-  <si>
-    <t>9D528428A211EA99EAD0031AEE178470</t>
-  </si>
-  <si>
-    <t>807253.15</t>
-  </si>
-  <si>
-    <t>31/07/2022</t>
-  </si>
-  <si>
-    <t>611768D07DCD09413D7BA226471E2D4D</t>
-  </si>
-  <si>
-    <t>117181</t>
-  </si>
-  <si>
-    <t>28/07/2022</t>
-  </si>
-  <si>
-    <t>CC6F3EC1E5C28226A4221E3FF2593443</t>
-  </si>
-  <si>
-    <t>29/07/2022</t>
-  </si>
-  <si>
-    <t>E645EEF9C385CEA4A027CD27BB3B737C</t>
-  </si>
-  <si>
-    <t>4A3FD975FB762687C6F6C8C0ACC54A4C</t>
-  </si>
-  <si>
-    <t>115729.75</t>
-  </si>
-  <si>
-    <t>EEE545579C3730B3F68D1AA0DB4F3845</t>
-  </si>
-  <si>
-    <t>8594405.5</t>
-  </si>
-  <si>
-    <t>13/09/2022</t>
-  </si>
-  <si>
-    <t>547C2DD2152E37BB87E16F05E20027FB</t>
-  </si>
-  <si>
-    <t>3038349.65</t>
-  </si>
-  <si>
-    <t>25A7C75D085581B96CB582A04394D75B</t>
-  </si>
-  <si>
-    <t>130135</t>
-  </si>
-  <si>
-    <t>09/09/2022</t>
-  </si>
-  <si>
-    <t>33E49E329E150BF044DEE68B1830602B</t>
-  </si>
-  <si>
-    <t>16092285</t>
-  </si>
-  <si>
-    <t>12/09/2022</t>
-  </si>
-  <si>
-    <t>CF6B1B3241FDB662C5399E7D1ABB445A</t>
-  </si>
-  <si>
-    <t>49282.22</t>
-  </si>
-  <si>
-    <t>31/08/2022</t>
-  </si>
-  <si>
-    <t>6124F961A9A76B5DC9760D829920F347</t>
-  </si>
-  <si>
-    <t>310957.62</t>
-  </si>
-  <si>
-    <t>01592C8B68D727BFFBE875E2E48B5846</t>
-  </si>
-  <si>
-    <t>3297610</t>
-  </si>
-  <si>
-    <t>23/08/2022</t>
-  </si>
-  <si>
-    <t>FBDD80D66FBA4C0B436EF25E72A8B6C6</t>
-  </si>
-  <si>
-    <t>D5EC5278C39CBE51C80E16DEF0378EBC</t>
-  </si>
-  <si>
-    <t>8D41560069B69B3F6704BD8745F4E6FC</t>
-  </si>
-  <si>
-    <t>56427.11</t>
-  </si>
-  <si>
-    <t>723EDCD4B1D458F3E6DD6FA90C8C337F</t>
-  </si>
-  <si>
-    <t>279751.82</t>
-  </si>
-  <si>
-    <t>22C64250C2389FA01C80DCB47493E607</t>
-  </si>
-  <si>
-    <t>7023672</t>
-  </si>
-  <si>
-    <t>CC1F7129015B85B20FF6FFA152C9CDB3</t>
-  </si>
-  <si>
-    <t>9EBD8E4E6303063CFCBCB302AAEC84DF</t>
-  </si>
-  <si>
-    <t>0F42D66D78B88C3484B5FD745BA0BE6D</t>
-  </si>
-  <si>
-    <t>115730.75</t>
-  </si>
-  <si>
-    <t>DC1B692677844EE01A7B3F0003D507D2</t>
-  </si>
-  <si>
-    <t>27/09/2022</t>
-  </si>
-  <si>
-    <t>33828BC802DA652922D812822F49363C</t>
-  </si>
-  <si>
-    <t>D1E71B4D9A6EE1B49F26EE67E2ACCEF6</t>
-  </si>
-  <si>
-    <t>117759.75</t>
-  </si>
-  <si>
-    <t>FB65C7ED665A874306DCAF9049709297</t>
-  </si>
-  <si>
-    <t>09/08/2022</t>
-  </si>
-  <si>
-    <t>C2F6FA154CC000A76A6239060A05C2C0</t>
-  </si>
-  <si>
-    <t>E560FF2A797A8D8460343F9A6DFC2542</t>
-  </si>
-  <si>
-    <t>42927.47</t>
-  </si>
-  <si>
-    <t>ADCDC7531699C1203F921E57BB085968</t>
-  </si>
-  <si>
-    <t>504174</t>
-  </si>
-  <si>
-    <t>00E47DC639FE7EE410FB278D892A69D9</t>
-  </si>
-  <si>
-    <t>10271234.5</t>
-  </si>
-  <si>
-    <t>B112BAC67D7FF8B1DAE8D33442765C6C</t>
-  </si>
-  <si>
-    <t>25/07/2022</t>
-  </si>
-  <si>
-    <t>79C3FA63AFBDA12B57D26B87501F1E88</t>
-  </si>
-  <si>
-    <t>22/07/2022</t>
-  </si>
-  <si>
-    <t>0E03A1FFDE601CECA2E9A06D4FD3218A</t>
-  </si>
-  <si>
-    <t>6138AB2ACD751B014157F9292118D57F</t>
-  </si>
-  <si>
-    <t>12/07/2022</t>
-  </si>
-  <si>
-    <t>AE5A896B134FC2D2F656DD46605D3136</t>
-  </si>
-  <si>
-    <t>25568853</t>
-  </si>
-  <si>
-    <t>11/07/2022</t>
+    <t>135980</t>
+  </si>
+  <si>
+    <t>26674055</t>
+  </si>
+  <si>
+    <t>21/07/2023</t>
+  </si>
+  <si>
+    <t>A31BE3F7B54203106BD0BA936D57E6C0</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>5938088</t>
+  </si>
+  <si>
+    <t>26/09/2023</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto.%20Programacion%20y%20Presupuesto/3er%20Trimestre/Informacion%20Presupuestal.pdf</t>
+  </si>
+  <si>
+    <t>17/10/2023</t>
+  </si>
+  <si>
+    <t>F2E235EB4FF99B3F78E1C38431C95878</t>
+  </si>
+  <si>
+    <t>27659.85</t>
+  </si>
+  <si>
+    <t>323AD347B6E29AE893E65E9948567270</t>
+  </si>
+  <si>
+    <t>61150</t>
+  </si>
+  <si>
+    <t>1BD7B3017214A9B6883718A885D91AD1</t>
+  </si>
+  <si>
+    <t>19479</t>
+  </si>
+  <si>
+    <t>FF9945E982C8A18C16EEDB57AA077C5B</t>
+  </si>
+  <si>
+    <t>11/07/2023</t>
+  </si>
+  <si>
+    <t>3564ECB79F4E967258226E576BD5DF4D</t>
+  </si>
+  <si>
+    <t>C92136ECB63A156EF2148FDE1F288EFB</t>
+  </si>
+  <si>
+    <t>17685</t>
+  </si>
+  <si>
+    <t>EBBF7826E643280E03022CE5568C284B</t>
+  </si>
+  <si>
+    <t>7930150.5</t>
+  </si>
+  <si>
+    <t>24/07/2023</t>
+  </si>
+  <si>
+    <t>293622AE744EAFF7F0455DBF7DC1A188</t>
+  </si>
+  <si>
+    <t>12019497</t>
+  </si>
+  <si>
+    <t>F20AB9E6EC8BF05DAC08216C53AE7500</t>
+  </si>
+  <si>
+    <t>6348922</t>
+  </si>
+  <si>
+    <t>84F56AD6D3B3B9925BFD083A690782B5</t>
+  </si>
+  <si>
+    <t>119666</t>
+  </si>
+  <si>
+    <t>B7614F4880F526BA9E5306701BF4A418</t>
+  </si>
+  <si>
+    <t>187357</t>
+  </si>
+  <si>
+    <t>27/07/2023</t>
+  </si>
+  <si>
+    <t>DB33DA055A620CE468D6FAE819E0E2F8</t>
+  </si>
+  <si>
+    <t>8286.59</t>
+  </si>
+  <si>
+    <t>30/07/2023</t>
+  </si>
+  <si>
+    <t>97A3604DCA5ECD40565203603BBD6085</t>
+  </si>
+  <si>
+    <t>236962</t>
+  </si>
+  <si>
+    <t>4D075A55FB852A004A0E398067FB45A6</t>
+  </si>
+  <si>
+    <t>14/08/2023</t>
+  </si>
+  <si>
+    <t>A39CDB5E5F8FD003F62FACB26F4CA8BE</t>
+  </si>
+  <si>
+    <t>12042470.5</t>
+  </si>
+  <si>
+    <t>15/08/2023</t>
+  </si>
+  <si>
+    <t>92D411D062DF6A0EBEB14B3B45C6F1A0</t>
+  </si>
+  <si>
+    <t>16787866</t>
+  </si>
+  <si>
+    <t>11/08/2023</t>
+  </si>
+  <si>
+    <t>F6F6CC9F8535F0E87C7CAC95BEB73EE2</t>
+  </si>
+  <si>
+    <t>1219376.75</t>
+  </si>
+  <si>
+    <t>4E77CA55173649717B5AEF1E3F16A4C9</t>
+  </si>
+  <si>
+    <t>2069462.25</t>
+  </si>
+  <si>
+    <t>30/08/2023</t>
+  </si>
+  <si>
+    <t>AA1887DA1A6E130CE4608B5A12B56175</t>
+  </si>
+  <si>
+    <t>4962405.5</t>
+  </si>
+  <si>
+    <t>B1705B50988C904326FB64997F146A9E</t>
+  </si>
+  <si>
+    <t>63179</t>
+  </si>
+  <si>
+    <t>3542E74FC807D2EA4FB4931D1DB7934D</t>
+  </si>
+  <si>
+    <t>5617775</t>
+  </si>
+  <si>
+    <t>D0D26D755F18D891CED249B000C872FF</t>
+  </si>
+  <si>
+    <t>76202</t>
+  </si>
+  <si>
+    <t>F676DB318291FA892577A988539963CA</t>
+  </si>
+  <si>
+    <t>25594.09</t>
+  </si>
+  <si>
+    <t>31/08/2023</t>
+  </si>
+  <si>
+    <t>9B784B6888B70CA7F6280C2CAB89B0C6</t>
+  </si>
+  <si>
+    <t>27970</t>
+  </si>
+  <si>
+    <t>8F34892A5D0A29DF6B08ABD343BEC450</t>
+  </si>
+  <si>
+    <t>14/09/2023</t>
+  </si>
+  <si>
+    <t>5347563F88D8A97D8E02D2222C8D3B7C</t>
+  </si>
+  <si>
+    <t>5448744.75</t>
+  </si>
+  <si>
+    <t>15/09/2023</t>
+  </si>
+  <si>
+    <t>B49FB802DE0BFFCA5CF90741BA90A210</t>
+  </si>
+  <si>
+    <t>1506410.25</t>
+  </si>
+  <si>
+    <t>AAB59412A83A64F9659EF33A4C197CD4</t>
+  </si>
+  <si>
+    <t>11/09/2023</t>
+  </si>
+  <si>
+    <t>590461D0F640D7B87ACD115E383828DB</t>
+  </si>
+  <si>
+    <t>6041529.25</t>
+  </si>
+  <si>
+    <t>B7EE885C92514B1472AA3FE08BF824C9</t>
+  </si>
+  <si>
+    <t>2099194.75</t>
+  </si>
+  <si>
+    <t>C04B9C2421BC4169E42797E1D780551E</t>
   </si>
 </sst>
 </file>
@@ -815,20 +814,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="76.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="47.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="58.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="185.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="181.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
@@ -1025,46 +1024,46 @@
     </row>
     <row r="8" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>48</v>
@@ -1072,46 +1071,46 @@
     </row>
     <row r="9" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>48</v>
@@ -1119,46 +1118,46 @@
     </row>
     <row r="10" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>48</v>
@@ -1166,46 +1165,46 @@
     </row>
     <row r="11" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>48</v>
@@ -1213,46 +1212,46 @@
     </row>
     <row r="12" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="J12" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>48</v>
@@ -1260,46 +1259,46 @@
     </row>
     <row r="13" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>75</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>48</v>
@@ -1307,46 +1306,46 @@
     </row>
     <row r="14" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>48</v>
@@ -1354,46 +1353,46 @@
     </row>
     <row r="15" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>48</v>
@@ -1401,46 +1400,46 @@
     </row>
     <row r="16" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>48</v>
@@ -1448,46 +1447,46 @@
     </row>
     <row r="17" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>48</v>
@@ -1495,46 +1494,46 @@
     </row>
     <row r="18" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>53</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>48</v>
@@ -1542,46 +1541,46 @@
     </row>
     <row r="19" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>48</v>
@@ -1589,46 +1588,46 @@
     </row>
     <row r="20" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>48</v>
@@ -1636,46 +1635,46 @@
     </row>
     <row r="21" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>48</v>
@@ -1683,46 +1682,46 @@
     </row>
     <row r="22" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="J22" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>48</v>
@@ -1730,46 +1729,46 @@
     </row>
     <row r="23" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>53</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>48</v>
@@ -1777,46 +1776,46 @@
     </row>
     <row r="24" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F24" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="I24" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>48</v>
@@ -1824,46 +1823,46 @@
     </row>
     <row r="25" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>48</v>
@@ -1871,46 +1870,46 @@
     </row>
     <row r="26" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>48</v>
@@ -1924,40 +1923,40 @@
         <v>42</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>48</v>
@@ -1965,46 +1964,46 @@
     </row>
     <row r="28" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>48</v>
@@ -2012,46 +2011,46 @@
     </row>
     <row r="29" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>48</v>
@@ -2059,46 +2058,46 @@
     </row>
     <row r="30" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>48</v>
@@ -2106,46 +2105,46 @@
     </row>
     <row r="31" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="J31" s="2" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>48</v>
@@ -2153,46 +2152,46 @@
     </row>
     <row r="32" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I32" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="J32" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>48</v>
@@ -2200,46 +2199,46 @@
     </row>
     <row r="33" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>48</v>
@@ -2247,46 +2246,46 @@
     </row>
     <row r="34" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>53</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>48</v>
@@ -2294,46 +2293,46 @@
     </row>
     <row r="35" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>48</v>
@@ -2341,46 +2340,46 @@
     </row>
     <row r="36" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>48</v>
@@ -2388,46 +2387,46 @@
     </row>
     <row r="37" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>127</v>
+        <v>65</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>48</v>
@@ -2435,46 +2434,46 @@
     </row>
     <row r="38" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>48</v>
@@ -2482,142 +2481,48 @@
     </row>
     <row r="39" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="O41" s="2" t="s">
         <v>48</v>
       </c>
     </row>
